--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/9_Variance/Exercises/2.9.+Variance_exercise - completed.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/9_Variance/Exercises/2.9.+Variance_exercise - completed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\365 Data Science\Statistics\Section 2\9_Variance\Exercises\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics\Section 2 - Descriptive Statistics Fundamentals\9_Variance\Exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8ABD0E-0798-4C77-92C8-CF3D42A67ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7379BD-6540-43E8-BB7F-1497292D400E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,13 +17,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Variance!$B$12:$B$22</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Variance!$B$12:$B$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -209,7 +211,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -791,15 +793,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:colOff>624840</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -835,8 +837,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1744980" y="4491990"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="1775460" y="4103370"/>
+              <a:ext cx="5501640" cy="2754630"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
